--- a/documents/shenzhen_air/交接单.xlsx
+++ b/documents/shenzhen_air/交接单.xlsx
@@ -2,14 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="普货和细胞" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,50 +26,366 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>陈志超</author>
+  </authors>
+  <commentList>
+    <comment ref="D4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+航班号</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+目的地名称</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+填航班日期</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+运单号</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+件数</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+重量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+计费重量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+包装</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+货物名称</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+件数</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+重量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+计费重量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+非必填；
+由业务员在新增运单时人工输入；</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>陈志超:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+固定内容输入，参数配置时填入；</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>ZH9929</t>
+    <t>ZH9505</t>
   </si>
   <si>
-    <t>济南</t>
+    <t>上海虹桥</t>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>479-53957562</t>
+  </si>
+  <si>
+    <t>纸箱</t>
+  </si>
+  <si>
+    <t>NK细胞</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>深航安检编号：74</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">         </t>
+      <t>航空公司同意运输证明  的填写条件：</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>√</t>
+      <t>运输细胞类货物</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-  </si>
-  <si>
-    <t>479-57515651</t>
-  </si>
-  <si>
-    <t>纸箱</t>
-  </si>
-  <si>
-    <t>拉链 背光源 鞋子 塑胶壳 海报 螺丝 线路板 服装 显示器 广告画 布匹 纸巾 数据线 鞋 内存卡 五金件 塑胶件 支撑架 画册 说明书 手机屏 贴膜 电源模块 五金模具 线材 (内含氧化银电池364SR621SW，根据特殊规定A123，不受限制）</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>唐文旭</t>
@@ -87,7 +401,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,23 +412,34 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -259,6 +584,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -566,153 +902,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -724,40 +1060,53 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -812,13 +1161,316 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>201930</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1270</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>336550</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>128270</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5801360" y="1270"/>
+          <a:ext cx="7010400" cy="9982200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>508635</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>489585</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>122555</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14218285" y="12700"/>
+          <a:ext cx="6153150" cy="7953375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1070,647 +1722,648 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J50"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="5.37962962962963" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.3796296296296" style="1"/>
+    <col min="3" max="3" width="10.8796296296296" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.62962962962963" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.87962962962963" style="1" customWidth="1"/>
+    <col min="11" max="13" width="9" style="1"/>
+    <col min="14" max="14" width="14.1296296296296" style="1"/>
+    <col min="15" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="14.1296296296296" style="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1" spans="1:10">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
+    <row r="1" spans="1:10">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+    <row r="2" ht="8" customHeight="1" spans="1:10">
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:10">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="4" t="s">
+    <row r="3" ht="12" customHeight="1"/>
+    <row r="4" ht="19" customHeight="1" spans="1:10">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5">
+      <c r="G4" s="5"/>
+      <c r="H4" s="6">
         <v>2025</v>
       </c>
-      <c r="I4" s="5">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="6" t="s">
+      <c r="I4" s="6">
         <v>2</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="J4" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:10">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="4">
-        <v>110</v>
+      <c r="B12" s="8"/>
+      <c r="C12" s="5">
+        <v>1</v>
       </c>
       <c r="D12" s="8">
-        <v>400</v>
+        <v>5</v>
       </c>
-      <c r="E12" s="4">
-        <v>600</v>
+      <c r="E12" s="5">
+        <v>5</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:10">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="4"/>
+    <row r="13" spans="1:10">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="11"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="10" t="s">
+      <c r="E13" s="11"/>
+      <c r="F13" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="6"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:10">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:10">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="11">
-        <v>110</v>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" ht="14" customHeight="1" spans="1:23">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="14">
+        <f>C12</f>
+        <v>1</v>
       </c>
-      <c r="D28" s="11">
-        <v>400</v>
+      <c r="D28" s="14">
+        <f>D12</f>
+        <v>5</v>
       </c>
-      <c r="E28" s="11">
-        <v>600</v>
+      <c r="E28" s="14">
+        <f>E12</f>
+        <v>5</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:10">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:10">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:10">
-      <c r="A47" s="1"/>
-      <c r="B47" s="15" t="s">
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:23">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:23">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="15"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="1"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" spans="1:23">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:23">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="V32" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="W32" s="17"/>
+    </row>
+    <row r="33" spans="1:23">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+    </row>
+    <row r="34" spans="1:23">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+    </row>
+    <row r="36" spans="1:23">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" ht="3" customHeight="1" spans="1:23">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" hidden="1" spans="1:23">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+    </row>
+    <row r="46" spans="1:23">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+    </row>
+    <row r="47" spans="1:23">
+      <c r="A47" s="4"/>
+      <c r="B47" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:23">
+      <c r="A48" s="4"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="1"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="G25:H25"/>
+  <mergeCells count="22">
+    <mergeCell ref="H30:J30"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="D12:D13"/>
@@ -1731,33 +2384,12 @@
     <mergeCell ref="C43:D46"/>
     <mergeCell ref="G43:J46"/>
     <mergeCell ref="B47:C49"/>
+    <mergeCell ref="V32:W35"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.904861111111111" right="0.590277777777778" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/documents/shenzhen_air/交接单.xlsx
+++ b/documents/shenzhen_air/交接单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="普货和细胞" sheetId="3" r:id="rId1"/>
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>ZH9505</t>
   </si>
@@ -370,22 +370,6 @@
   </si>
   <si>
     <t>深航安检编号：74</t>
-  </si>
-  <si>
-    <r>
-      <t>航空公司同意运输证明  的填写条件：</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>运输细胞类货物</t>
-    </r>
   </si>
   <si>
     <t>唐文旭</t>
@@ -1047,7 +1031,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1090,9 +1074,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1382,95 +1363,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>201930</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>1270</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>336550</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>128270</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5801360" y="1270"/>
-          <a:ext cx="7010400" cy="9982200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>508635</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>489585</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>122555</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14218285" y="12700"/>
-          <a:ext cx="6153150" cy="7953375"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2115,11 +2007,11 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="15" t="s">
+      <c r="H30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
     </row>
     <row r="31" spans="1:23">
       <c r="A31" s="4"/>
@@ -2136,46 +2028,44 @@
     <row r="32" spans="1:23">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="V32" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="W32" s="17"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="16"/>
     </row>
     <row r="33" spans="1:23">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="V33" s="16"/>
+      <c r="W33" s="16"/>
     </row>
     <row r="34" spans="1:23">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
     </row>
     <row r="35" spans="1:23">
       <c r="A35" s="4"/>
@@ -2188,8 +2078,8 @@
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="16"/>
     </row>
     <row r="36" spans="1:23">
       <c r="A36" s="4"/>
@@ -2278,57 +2168,57 @@
     <row r="43" spans="1:23">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="19"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="18"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
     </row>
     <row r="44" spans="1:23">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
     </row>
     <row r="45" spans="1:23">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
     </row>
     <row r="46" spans="1:23">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
     </row>
     <row r="47" spans="1:23">
       <c r="A47" s="4"/>
-      <c r="B47" s="20" t="s">
-        <v>9</v>
+      <c r="B47" s="19" t="s">
+        <v>8</v>
       </c>
-      <c r="C47" s="20"/>
+      <c r="C47" s="19"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -2339,8 +2229,8 @@
     </row>
     <row r="48" spans="1:23">
       <c r="A48" s="4"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -2351,8 +2241,8 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -2389,7 +2279,6 @@
   <pageMargins left="0.904861111111111" right="0.590277777777778" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/documents/shenzhen_air/交接单.xlsx
+++ b/documents/shenzhen_air/交接单.xlsx
@@ -24,325 +24,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>陈志超</author>
-  </authors>
-  <commentList>
-    <comment ref="D4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-航班号</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-目的地名称</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-填航班日期</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-运单号</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-件数</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-重量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-计费重量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-包装</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-货物名称</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C28" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-件数</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D28" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-重量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E28" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-计费重量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H30" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-非必填；
-由业务员在新增运单时人工输入；</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B47" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-固定内容输入，参数配置时填入；</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -385,7 +66,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,7 +77,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -404,7 +84,6 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -412,15 +91,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -568,17 +238,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -901,137 +560,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1044,50 +703,44 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1653,603 +1306,280 @@
     </row>
     <row r="3" ht="12" customHeight="1"/>
     <row r="4" ht="19" customHeight="1" spans="1:10">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6">
+      <c r="G4" s="4"/>
+      <c r="H4" s="5">
         <v>2025</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>2</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="5">
+      <c r="B12" s="7"/>
+      <c r="C12" s="4">
         <v>1</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>5</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>5</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="10" t="s">
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="12" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="10"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="10"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="4"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:23">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:23">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:23">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:23">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:23">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:23">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:23">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:23">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:23">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:23">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:23">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" ht="14" customHeight="1" spans="1:23">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="14">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="3:23">
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="3:23">
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="3:23">
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="3:23">
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="3:23">
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="3:23">
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="3:23">
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="3:23">
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="3:23">
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+    </row>
+    <row r="28" ht="14" customHeight="1" spans="3:23">
+      <c r="C28" s="13">
         <f>C12</f>
         <v>1</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13">
         <f>D12</f>
         <v>5</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="13">
         <f>E12</f>
         <v>5</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:23">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:23">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="10" t="s">
+    </row>
+    <row r="29" spans="3:23">
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+    </row>
+    <row r="30" spans="3:23">
+      <c r="H30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-    </row>
-    <row r="31" spans="1:23">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:23">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-    </row>
-    <row r="33" spans="1:23">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-    </row>
-    <row r="34" spans="1:23">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-    </row>
-    <row r="35" spans="1:23">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
-    </row>
-    <row r="36" spans="1:23">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:23">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-    </row>
-    <row r="38" ht="3" customHeight="1" spans="1:23">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:23">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:23">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-    </row>
-    <row r="41" hidden="1" spans="1:23">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:23">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:23">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-    </row>
-    <row r="44" spans="1:23">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-    </row>
-    <row r="45" spans="1:23">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-    </row>
-    <row r="46" spans="1:23">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-    </row>
-    <row r="47" spans="1:23">
-      <c r="A47" s="4"/>
-      <c r="B47" s="19" t="s">
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="32" spans="3:23">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="V32" s="15"/>
+      <c r="W32" s="15"/>
+    </row>
+    <row r="33" spans="2:23">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+    </row>
+    <row r="34" spans="2:23">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+    </row>
+    <row r="35" spans="2:23">
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+    </row>
+    <row r="38" ht="3" customHeight="1"/>
+    <row r="41" hidden="1"/>
+    <row r="43" spans="2:23">
+      <c r="C43" s="15"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" spans="2:23">
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+    </row>
+    <row r="45" spans="2:23">
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+    </row>
+    <row r="46" spans="2:23">
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+    </row>
+    <row r="47" spans="2:23">
+      <c r="B47" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="19"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="1:23">
-      <c r="A48" s="4"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="4"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
+      <c r="C47" s="17"/>
+    </row>
+    <row r="48" spans="2:23">
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+    </row>
+    <row r="49" spans="2:3">
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -2279,6 +1609,5 @@
   <pageMargins left="0.904861111111111" right="0.590277777777778" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/documents/shenzhen_air/交接单.xlsx
+++ b/documents/shenzhen_air/交接单.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>ZH9505</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>深航安检编号：74</t>
   </si>
   <si>
     <t>唐文旭</t>
@@ -1396,10 +1393,6 @@
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
@@ -1479,9 +1472,7 @@
       <c r="E29" s="13"/>
     </row>
     <row r="30" spans="3:23">
-      <c r="H30" s="9" t="s">
-        <v>7</v>
-      </c>
+      <c r="H30" s="9"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
     </row>
@@ -1530,8 +1521,6 @@
     <row r="43" spans="2:23">
       <c r="C43" s="15"/>
       <c r="D43" s="16"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
       <c r="G43" s="15"/>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
@@ -1540,8 +1529,6 @@
     <row r="44" spans="2:23">
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
       <c r="G44" s="15"/>
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
@@ -1550,8 +1537,6 @@
     <row r="45" spans="2:23">
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
       <c r="G45" s="15"/>
       <c r="H45" s="15"/>
       <c r="I45" s="15"/>
@@ -1560,8 +1545,6 @@
     <row r="46" spans="2:23">
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="15"/>
@@ -1569,7 +1552,7 @@
     </row>
     <row r="47" spans="2:23">
       <c r="B47" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" s="17"/>
     </row>

--- a/documents/shenzhen_air/交接单.xlsx
+++ b/documents/shenzhen_air/交接单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="32400" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="普货和细胞" sheetId="3" r:id="rId1"/>
@@ -687,7 +687,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -730,6 +730,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1266,22 +1269,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:W49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.37962962962963" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.3796296296296" style="1"/>
-    <col min="3" max="3" width="10.8796296296296" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.38333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.3833333333333" style="1"/>
+    <col min="3" max="3" width="10.8833333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.62962962962963" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.63333333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
     <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="6.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="6.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.87962962962963" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.88333333333333" style="1" customWidth="1"/>
     <col min="11" max="13" width="9" style="1"/>
-    <col min="14" max="14" width="14.1296296296296" style="1"/>
+    <col min="14" max="14" width="14.1333333333333" style="1"/>
     <col min="15" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="14.1296296296296" style="1"/>
+    <col min="18" max="18" width="14.1333333333333" style="1"/>
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1519,53 +1522,53 @@
     <row r="38" ht="3" customHeight="1"/>
     <row r="41" hidden="1"/>
     <row r="43" spans="2:23">
-      <c r="C43" s="15"/>
-      <c r="D43" s="16"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="17"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
     </row>
     <row r="44" spans="2:23">
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
     </row>
     <row r="45" spans="2:23">
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
     </row>
     <row r="46" spans="2:23">
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
     </row>
     <row r="47" spans="2:23">
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="17"/>
+      <c r="C47" s="18"/>
     </row>
     <row r="48" spans="2:23">
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
     </row>
     <row r="49" spans="2:3">
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="21">
     <mergeCell ref="H30:J30"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="C28:C29"/>
@@ -1587,7 +1590,6 @@
     <mergeCell ref="C43:D46"/>
     <mergeCell ref="G43:J46"/>
     <mergeCell ref="B47:C49"/>
-    <mergeCell ref="V32:W35"/>
   </mergeCells>
   <pageMargins left="0.904861111111111" right="0.590277777777778" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
